--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -668,7 +668,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>dateAutorisation</t>
+    <t>ActiviteSociale.dateAutorisation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.id</t>
@@ -780,7 +780,7 @@
 per-1</t>
   </si>
   <si>
-    <t>datePremiereInstallation</t>
+    <t>ActiviteSociale.datePremiereInstallation</t>
   </si>
   <si>
     <t>./low</t>
@@ -837,7 +837,7 @@
     <t>deleteAuthorization</t>
   </si>
   <si>
-    <t>suppressionAutorisation</t>
+    <t>ActiviteSociale.suppressionAutorisation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.id</t>
@@ -883,7 +883,7 @@
     <t>deleteInstallation</t>
   </si>
   <si>
-    <t>suppressionInstallation</t>
+    <t>ActiviteSociale.suppressionInstallation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.id</t>
@@ -1024,7 +1024,7 @@
 qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
-    <t>ageMinAutorisee</t>
+    <t>ActiviteSociale.ageMinAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:authorizedAgeRange.value[x].high</t>
@@ -1045,7 +1045,7 @@
     <t>Range.high</t>
   </si>
   <si>
-    <t>ageMaxAutorisee</t>
+    <t>ActiviteSociale.ageMaxAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange</t>
@@ -1075,7 +1075,7 @@
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange.value[x].low</t>
   </si>
   <si>
-    <t>ageMaxInstallee</t>
+    <t>ActiviteSociale.ageMaxInstallee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange.value[x].high</t>
@@ -1118,7 +1118,7 @@
     <t>capacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutorisee</t>
+    <t>ActiviteSociale.capaciteAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:capacityAvailable.id</t>
@@ -1143,7 +1143,7 @@
     <t>femaleCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeFemme</t>
+    <t>ActiviteSociale.capaciteAutoriseeFemme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:femaleCapacityAvailable.id</t>
@@ -1164,7 +1164,7 @@
     <t>maleCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeHomme</t>
+    <t>ActiviteSociale.capaciteAutoriseeHomme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:maleCapacityAvailable.id</t>
@@ -1185,7 +1185,7 @@
     <t>socialAssistanceCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeHabiliteAideSociale</t>
+    <t>ActiviteSociale.capaciteAutoriseeHabiliteAideSociale</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:socialAssistanceCapacityAvailable.id</t>
@@ -1206,7 +1206,7 @@
     <t>installedCapacity</t>
   </si>
   <si>
-    <t>capaciteInstallee</t>
+    <t>ActiviteSociale.capaciteInstallee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:installedCapacity.id</t>
@@ -1227,7 +1227,7 @@
     <t>femaleInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeFemme</t>
+    <t>ActiviteSociale.capaciteInstalleeFemme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:femaleInstalledCapacity.id</t>
@@ -1248,7 +1248,7 @@
     <t>maleInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeHomme</t>
+    <t>ActiviteSociale.capaciteInstalleeHomme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:maleInstalledCapacity.id</t>
@@ -1269,7 +1269,7 @@
     <t>socialAssistanceInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeHabiliteAideSociale</t>
+    <t>ActiviteSociale.capaciteInstalleeHabiliteAideSociale</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:socialAssistanceInstalledCapacity.id</t>
@@ -1609,7 +1609,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
   </si>
   <si>
-    <t>discipineEquipementSociale</t>
+    <t>ActiviteSociale.discipineEquipementSociale</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -1828,7 +1828,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J137-Clientele-RASS/FHIR/JDV-J137-Clientele-RASS</t>
   </si>
   <si>
-    <t>clientele</t>
+    <t>ActiviteSociale.clientele</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.comment</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
